--- a/RaidenDemo/文档/配置表/BulletResource.xlsx
+++ b/RaidenDemo/文档/配置表/BulletResource.xlsx
@@ -2256,7 +2256,7 @@
         <v>1600</v>
       </c>
       <c r="O15" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P15" s="7"/>
       <c r="Q15" s="7"/>
@@ -2554,10 +2554,10 @@
         <v>0</v>
       </c>
       <c r="N22" s="7">
-        <v>800</v>
+        <v>2000</v>
       </c>
       <c r="O22" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P22" s="7"/>
       <c r="Q22" s="7"/>
